--- a/reports/pdf_change_20260728.xlsx
+++ b/reports/pdf_change_20260728.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,032억   ·   현금 24억(0.6%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,141억   ·   현금 24억(0.6%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>426545280</v>
+        <v>425687040</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-25</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-408037000</v>
+        <v>-407216000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>391387500</v>
+        <v>390600000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-22</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-287126840</v>
+        <v>-286549120</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>780687600</v>
+        <v>779116800</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-390244400</v>
+        <v>-389459200</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,527억   ·   현금 13억(0.4%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,519억   ·   현금 13억(0.4%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -819,7 +819,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,302억   ·   현금 37억(1.6%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 4종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,359억   ·   현금 37억(1.6%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -915,7 +915,7 @@
         <v>26</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>426410400</v>
+        <v>425178000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>-110</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-4673768000</v>
+        <v>-4660260000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>4749888000</v>
+        <v>4736160000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>-20</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1966664000</v>
+        <v>-1960980000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1234528000</v>
+        <v>1230960000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>-3</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-167325600</v>
+        <v>-166842000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>77642400</v>
+        <v>77418000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,238억   ·   현금 8억(0.4%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,030억   ·   현금 8억(0.4%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1092,7 +1092,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 1억(0.3%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 1억(0.3%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1188,7 +1188,7 @@
         <v>62</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>15337560</v>
+        <v>15502480</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1209,11 +1209,11 @@
         <v>-8</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-36236800</v>
+        <v>-35872000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.51%</t>
+          <t>0.63%→0.50%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -1232,11 +1232,11 @@
         <v>49</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>70756000</v>
+        <v>69564320</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>3.10%→3.37%</t>
+          <t>3.01%→3.27%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1253,7 +1253,7 @@
         <v>-7</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-51125200</v>
+        <v>-51923200</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
         <v>13</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>24354200</v>
+        <v>25688000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>0.69%→0.78%</t>
+          <t>0.72%→0.81%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1297,11 +1297,11 @@
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-68514000</v>
+        <v>-71136000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>1.71%→1.46%</t>
+          <t>1.75%→1.49%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 470억   ·   현금 3억(0.7%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 468억   ·   현금 3억(0.7%)      당일 2026-07-28  vs  전영업일 2026-07-27      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
